--- a/information_request_forms/023_offer_acknowledgment_form--information_request_forms.xlsx
+++ b/information_request_forms/023_offer_acknowledgment_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>full_time</t>
+          <t>full time</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>part_time</t>
+          <t>part time</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>team_member</t>
+          <t>team member</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>team_lead</t>
+          <t>team lead</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>high_school</t>
+          <t>high school</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0_2_years</t>
+          <t>0 2 years</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2_5_years</t>
+          <t>2 5 years</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5_10_years</t>
+          <t>5 10 years</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>less_than_3_years</t>
+          <t>less than 3 years</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3_to_10_years</t>
+          <t>3 to 10 years</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>more_than_10_years</t>
+          <t>more than 10 years</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>less_than_3_years</t>
+          <t>less than 3 years</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3_to_5_years</t>
+          <t>3 to 5 years</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>more_than_5_years</t>
+          <t>more than 5 years</t>
         </is>
       </c>
     </row>
